--- a/크아템.xlsx
+++ b/크아템.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishod\OneDrive\바탕 화면\비밀~\크아\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF468D33-C172-415E-A644-6FDA1D82A666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B7F96-257E-4A10-84ED-F19749761214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="3195" windowWidth="16005" windowHeight="12525" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
+    <workbookView xWindow="1356" yWindow="2220" windowWidth="17280" windowHeight="9960" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
   </bookViews>
   <sheets>
     <sheet name="판매" sheetId="2" r:id="rId1"/>
@@ -464,7 +464,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,12 +474,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,12 +641,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -989,31 +977,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A858C0A-06B6-49A2-8F0D-5E0ADD48EB1E}">
   <dimension ref="B1:S29"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.25" style="10" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="10" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.25" style="10" customWidth="1"/>
-    <col min="10" max="10" width="16.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="10" customWidth="1"/>
-    <col min="12" max="12" width="16.875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="10" customWidth="1"/>
-    <col min="14" max="14" width="16.875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.25" style="10" customWidth="1"/>
-    <col min="16" max="16" width="16.875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.25" style="10" customWidth="1"/>
-    <col min="18" max="18" width="16.875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.25" style="10" customWidth="1"/>
+    <col min="1" max="1" width="0.69921875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.8984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.8984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="16.8984375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.8984375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.19921875" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.8984375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="16.8984375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.19921875" style="10" customWidth="1"/>
+    <col min="16" max="16" width="16.8984375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.19921875" style="10" customWidth="1"/>
+    <col min="18" max="18" width="16.8984375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.19921875" style="10" customWidth="1"/>
     <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:19" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="1"/>
@@ -1033,7 +1021,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
@@ -1071,7 +1059,7 @@
       </c>
       <c r="S2" s="18"/>
     </row>
-    <row r="3" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1115,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
@@ -1183,7 +1171,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
@@ -1196,10 +1184,10 @@
       <c r="E5" s="7">
         <v>5000</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="15">
         <v>38000</v>
       </c>
       <c r="H5" s="6" t="s">
@@ -1235,7 +1223,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1286,7 +1274,7 @@
       </c>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
@@ -1317,10 +1305,10 @@
       <c r="K7" s="7">
         <v>3000</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="15">
         <v>5000</v>
       </c>
       <c r="O7" s="7"/>
@@ -1332,7 +1320,7 @@
       </c>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>81</v>
       </c>
@@ -1370,7 +1358,7 @@
       </c>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>60</v>
       </c>
@@ -1404,7 +1392,7 @@
       </c>
       <c r="S9" s="7"/>
     </row>
-    <row r="10" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>61</v>
       </c>
@@ -1439,7 +1427,7 @@
       </c>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>62</v>
       </c>
@@ -1475,7 +1463,7 @@
       <c r="R11" s="6"/>
       <c r="S11" s="7"/>
     </row>
-    <row r="12" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>82</v>
       </c>
@@ -1511,7 +1499,7 @@
       <c r="R12" s="6"/>
       <c r="S12" s="7"/>
     </row>
-    <row r="13" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
       <c r="D13" s="6" t="s">
@@ -1543,7 +1531,7 @@
       <c r="R13" s="6"/>
       <c r="S13" s="7"/>
     </row>
-    <row r="14" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="6" t="s">
@@ -1575,7 +1563,7 @@
       <c r="R14" s="6"/>
       <c r="S14" s="7"/>
     </row>
-    <row r="15" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6" t="s">
@@ -1607,7 +1595,7 @@
       <c r="R15" s="6"/>
       <c r="S15" s="7"/>
     </row>
-    <row r="16" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="6" t="s">
@@ -1629,7 +1617,7 @@
       <c r="R16" s="6"/>
       <c r="S16" s="7"/>
     </row>
-    <row r="17" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6" t="s">
@@ -1657,7 +1645,7 @@
       <c r="R17" s="6"/>
       <c r="S17" s="7"/>
     </row>
-    <row r="18" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6" t="s">
@@ -1681,7 +1669,7 @@
       <c r="R18" s="6"/>
       <c r="S18" s="7"/>
     </row>
-    <row r="19" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="6" t="s">
@@ -1705,7 +1693,7 @@
       <c r="R19" s="6"/>
       <c r="S19" s="7"/>
     </row>
-    <row r="20" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
       <c r="D20" s="6" t="s">
@@ -1729,7 +1717,7 @@
       <c r="R20" s="6"/>
       <c r="S20" s="7"/>
     </row>
-    <row r="21" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6"/>
@@ -1747,7 +1735,7 @@
       <c r="R21" s="6"/>
       <c r="S21" s="7"/>
     </row>
-    <row r="22" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
       <c r="D22" s="6"/>
@@ -1767,7 +1755,7 @@
       <c r="R22" s="6"/>
       <c r="S22" s="7"/>
     </row>
-    <row r="23" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
       <c r="D23" s="6"/>
@@ -1787,7 +1775,7 @@
       <c r="R23" s="6"/>
       <c r="S23" s="7"/>
     </row>
-    <row r="24" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6"/>
@@ -1807,7 +1795,7 @@
       <c r="R24" s="6"/>
       <c r="S24" s="7"/>
     </row>
-    <row r="25" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
       <c r="D25" s="6"/>
@@ -1827,7 +1815,7 @@
       <c r="R25" s="6"/>
       <c r="S25" s="7"/>
     </row>
-    <row r="26" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
       <c r="C26" s="9">
         <f>SUM(C4:C25)</f>
@@ -1874,7 +1862,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="29" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>59</v>
       </c>
@@ -1903,32 +1891,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6722EA2-97A1-4BCC-A637-4AF3548A6DFC}">
   <dimension ref="B1:T29"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.25" style="10" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="10" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.25" style="10" customWidth="1"/>
-    <col min="10" max="10" width="16.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="10" customWidth="1"/>
-    <col min="12" max="12" width="16.875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.25" style="10" customWidth="1"/>
-    <col min="14" max="14" width="16.875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.25" style="10" customWidth="1"/>
-    <col min="16" max="16" width="16.875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.25" style="10" customWidth="1"/>
-    <col min="18" max="18" width="2.25" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.875" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11.125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="0.69921875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.8984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.8984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="16.8984375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.8984375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.19921875" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.8984375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="16.8984375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.19921875" style="10" customWidth="1"/>
+    <col min="16" max="16" width="16.8984375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.19921875" style="10" customWidth="1"/>
+    <col min="18" max="18" width="2.19921875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.8984375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.09765625" style="10" customWidth="1"/>
     <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="1"/>
@@ -1948,7 +1936,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
@@ -1986,7 +1974,7 @@
       </c>
       <c r="T2" s="18"/>
     </row>
-    <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2042,7 +2030,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
@@ -2098,7 +2086,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
@@ -2154,7 +2142,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
@@ -2206,7 +2194,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
@@ -2254,7 +2242,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
@@ -2302,7 +2290,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="6" t="s">
@@ -2334,7 +2322,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
@@ -2362,7 +2350,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
       <c r="D11" s="6"/>
@@ -2386,7 +2374,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
       <c r="D12" s="6"/>
@@ -2406,7 +2394,7 @@
       <c r="S12" s="6"/>
       <c r="T12" s="7"/>
     </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
       <c r="D13" s="6"/>
@@ -2426,7 +2414,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="7"/>
     </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="6"/>
@@ -2446,7 +2434,7 @@
       <c r="S14" s="6"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6"/>
@@ -2466,7 +2454,7 @@
       <c r="S15" s="6"/>
       <c r="T15" s="7"/>
     </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="6"/>
@@ -2486,7 +2474,7 @@
       <c r="S16" s="6"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
@@ -2506,7 +2494,7 @@
       <c r="S17" s="6"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
@@ -2526,7 +2514,7 @@
       <c r="S18" s="6"/>
       <c r="T18" s="7"/>
     </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="6"/>
@@ -2546,7 +2534,7 @@
       <c r="S19" s="6"/>
       <c r="T19" s="7"/>
     </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
       <c r="D20" s="6"/>
@@ -2566,7 +2554,7 @@
       <c r="S20" s="6"/>
       <c r="T20" s="7"/>
     </row>
-    <row r="21" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6"/>
@@ -2586,7 +2574,7 @@
       <c r="S21" s="6"/>
       <c r="T21" s="7"/>
     </row>
-    <row r="22" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
       <c r="D22" s="6"/>
@@ -2606,7 +2594,7 @@
       <c r="S22" s="6"/>
       <c r="T22" s="7"/>
     </row>
-    <row r="23" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
       <c r="D23" s="6"/>
@@ -2626,7 +2614,7 @@
       <c r="S23" s="6"/>
       <c r="T23" s="7"/>
     </row>
-    <row r="24" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6"/>
@@ -2646,7 +2634,7 @@
       <c r="S24" s="6"/>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
       <c r="D25" s="6"/>
@@ -2666,7 +2654,7 @@
       <c r="S25" s="6"/>
       <c r="T25" s="7"/>
     </row>
-    <row r="26" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
       <c r="C26" s="9">
         <f>SUM(C4:C25)</f>
@@ -2714,7 +2702,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="29" spans="2:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>58</v>
       </c>

--- a/크아템.xlsx
+++ b/크아템.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B7F96-257E-4A10-84ED-F19749761214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB028319-796A-4C94-B440-57A7AAB7CCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1356" yWindow="2220" windowWidth="17280" windowHeight="9960" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
   </bookViews>
   <sheets>
     <sheet name="판매" sheetId="2" r:id="rId1"/>
@@ -473,7 +473,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,6 +627,12 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -634,12 +640,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1022,42 +1022,42 @@
       <c r="S1" s="2"/>
     </row>
     <row r="2" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="17" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="17" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="N2" s="17" t="s">
+      <c r="M2" s="15"/>
+      <c r="N2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="O2" s="18"/>
-      <c r="P2" s="17" t="s">
+      <c r="O2" s="15"/>
+      <c r="P2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="17" t="s">
+      <c r="Q2" s="15"/>
+      <c r="R2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="18"/>
+      <c r="S2" s="15"/>
     </row>
     <row r="3" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -1184,10 +1184,10 @@
       <c r="E5" s="7">
         <v>5000</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="17">
         <v>38000</v>
       </c>
       <c r="H5" s="6" t="s">
@@ -1208,10 +1208,10 @@
       <c r="M5" s="7">
         <v>5000</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="17">
         <v>5000</v>
       </c>
       <c r="P5" s="6" t="s">
@@ -1236,10 +1236,10 @@
       <c r="E6" s="7">
         <v>16000</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="17">
         <v>12000</v>
       </c>
       <c r="H6" s="6" t="s">
@@ -1305,10 +1305,10 @@
       <c r="K7" s="7">
         <v>3000</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="17">
         <v>5000</v>
       </c>
       <c r="O7" s="7"/>
@@ -1365,11 +1365,11 @@
       <c r="C9" s="7">
         <v>11000</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="7">
-        <v>20000</v>
+      <c r="E9" s="17">
+        <v>16000</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
@@ -1636,10 +1636,10 @@
       <c r="M17" s="7"/>
       <c r="N17" s="6"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="14" t="s">
+      <c r="P17" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="17">
         <v>14000</v>
       </c>
       <c r="R17" s="6"/>
@@ -1824,7 +1824,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="9">
         <f>SUM(E4:E25)</f>
-        <v>88500</v>
+        <v>84500</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C29" s="13">
         <f>SUM(B26:S26)</f>
-        <v>391000</v>
+        <v>387000</v>
       </c>
     </row>
   </sheetData>
@@ -1937,42 +1937,42 @@
       <c r="T1" s="2"/>
     </row>
     <row r="2" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="15"/>
+      <c r="F2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="17" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="17" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="N2" s="17" t="s">
+      <c r="M2" s="15"/>
+      <c r="N2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="18"/>
-      <c r="P2" s="17" t="s">
+      <c r="O2" s="15"/>
+      <c r="P2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="S2" s="17" t="s">
+      <c r="Q2" s="15"/>
+      <c r="S2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="18"/>
+      <c r="T2" s="15"/>
     </row>
     <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">

--- a/크아템.xlsx
+++ b/크아템.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B7F96-257E-4A10-84ED-F19749761214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03ADA1A4-95D9-4592-ADB1-3F29DDA55D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1356" yWindow="2220" windowWidth="17280" windowHeight="9960" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
   </bookViews>
   <sheets>
     <sheet name="판매" sheetId="2" r:id="rId1"/>
@@ -473,7 +473,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -977,31 +977,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A858C0A-06B6-49A2-8F0D-5E0ADD48EB1E}">
   <dimension ref="B1:S29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="0.69921875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.19921875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.8984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="16.8984375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="16.8984375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.19921875" style="10" customWidth="1"/>
-    <col min="12" max="12" width="16.8984375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="16.8984375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.19921875" style="10" customWidth="1"/>
-    <col min="16" max="16" width="16.8984375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.19921875" style="10" customWidth="1"/>
-    <col min="18" max="18" width="16.8984375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="9.19921875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="0.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.25" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.25" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="10" customWidth="1"/>
+    <col min="14" max="14" width="16.875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.25" style="10" customWidth="1"/>
+    <col min="16" max="16" width="16.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.25" style="10" customWidth="1"/>
+    <col min="18" max="18" width="16.875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.25" style="10" customWidth="1"/>
     <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:19" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="1"/>
@@ -1021,7 +1021,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="S2" s="18"/>
     </row>
-    <row r="3" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
@@ -1223,7 +1223,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="6" t="s">
         <v>81</v>
       </c>
@@ -1358,18 +1358,18 @@
       </c>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="6" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="7">
         <v>11000</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="7">
-        <v>20000</v>
+      <c r="E9" s="15">
+        <v>16000</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="S9" s="7"/>
     </row>
-    <row r="10" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="6" t="s">
         <v>61</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>76</v>
       </c>
       <c r="M10" s="7">
-        <v>12000</v>
+        <v>7000</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="7"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="6" t="s">
         <v>62</v>
       </c>
@@ -1463,7 +1463,7 @@
       <c r="R11" s="6"/>
       <c r="S11" s="7"/>
     </row>
-    <row r="12" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="6" t="s">
         <v>82</v>
       </c>
@@ -1499,7 +1499,7 @@
       <c r="R12" s="6"/>
       <c r="S12" s="7"/>
     </row>
-    <row r="13" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
       <c r="D13" s="6" t="s">
@@ -1531,7 +1531,7 @@
       <c r="R13" s="6"/>
       <c r="S13" s="7"/>
     </row>
-    <row r="14" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="6" t="s">
@@ -1563,7 +1563,7 @@
       <c r="R14" s="6"/>
       <c r="S14" s="7"/>
     </row>
-    <row r="15" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6" t="s">
@@ -1595,7 +1595,7 @@
       <c r="R15" s="6"/>
       <c r="S15" s="7"/>
     </row>
-    <row r="16" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="6" t="s">
@@ -1617,7 +1617,7 @@
       <c r="R16" s="6"/>
       <c r="S16" s="7"/>
     </row>
-    <row r="17" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6" t="s">
@@ -1645,7 +1645,7 @@
       <c r="R17" s="6"/>
       <c r="S17" s="7"/>
     </row>
-    <row r="18" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6" t="s">
@@ -1669,7 +1669,7 @@
       <c r="R18" s="6"/>
       <c r="S18" s="7"/>
     </row>
-    <row r="19" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="6" t="s">
@@ -1693,7 +1693,7 @@
       <c r="R19" s="6"/>
       <c r="S19" s="7"/>
     </row>
-    <row r="20" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
       <c r="D20" s="6" t="s">
@@ -1717,7 +1717,7 @@
       <c r="R20" s="6"/>
       <c r="S20" s="7"/>
     </row>
-    <row r="21" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6"/>
@@ -1735,7 +1735,7 @@
       <c r="R21" s="6"/>
       <c r="S21" s="7"/>
     </row>
-    <row r="22" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
       <c r="D22" s="6"/>
@@ -1755,7 +1755,7 @@
       <c r="R22" s="6"/>
       <c r="S22" s="7"/>
     </row>
-    <row r="23" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
       <c r="D23" s="6"/>
@@ -1775,7 +1775,7 @@
       <c r="R23" s="6"/>
       <c r="S23" s="7"/>
     </row>
-    <row r="24" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6"/>
@@ -1795,7 +1795,7 @@
       <c r="R24" s="6"/>
       <c r="S24" s="7"/>
     </row>
-    <row r="25" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
       <c r="D25" s="6"/>
@@ -1815,7 +1815,7 @@
       <c r="R25" s="6"/>
       <c r="S25" s="7"/>
     </row>
-    <row r="26" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="8"/>
       <c r="C26" s="9">
         <f>SUM(C4:C25)</f>
@@ -1824,7 +1824,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="9">
         <f>SUM(E4:E25)</f>
-        <v>88500</v>
+        <v>84500</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9">
@@ -1844,7 +1844,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="9">
         <f>SUM(M4:M25)</f>
-        <v>69500</v>
+        <v>64500</v>
       </c>
       <c r="N26" s="8"/>
       <c r="O26" s="9">
@@ -1862,13 +1862,13 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="29" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="13">
         <f>SUM(B26:S26)</f>
-        <v>391000</v>
+        <v>382000</v>
       </c>
     </row>
   </sheetData>
@@ -1891,32 +1891,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6722EA2-97A1-4BCC-A637-4AF3548A6DFC}">
   <dimension ref="B1:T29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="0.69921875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.19921875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.8984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="16.8984375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="16.8984375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.19921875" style="10" customWidth="1"/>
-    <col min="12" max="12" width="16.8984375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="16.8984375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.19921875" style="10" customWidth="1"/>
-    <col min="16" max="16" width="16.8984375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.19921875" style="10" customWidth="1"/>
-    <col min="18" max="18" width="2.19921875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.8984375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="11.09765625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="0.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="10" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.25" style="10" customWidth="1"/>
+    <col min="10" max="10" width="16.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.25" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.25" style="10" customWidth="1"/>
+    <col min="14" max="14" width="16.875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.25" style="10" customWidth="1"/>
+    <col min="16" max="16" width="16.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.25" style="10" customWidth="1"/>
+    <col min="18" max="18" width="2.25" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.125" style="10" customWidth="1"/>
     <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="1"/>
@@ -1936,7 +1936,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="T2" s="18"/>
     </row>
-    <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="6" t="s">
@@ -2322,7 +2322,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
@@ -2350,7 +2350,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
       <c r="D11" s="6"/>
@@ -2374,7 +2374,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
       <c r="D12" s="6"/>
@@ -2394,7 +2394,7 @@
       <c r="S12" s="6"/>
       <c r="T12" s="7"/>
     </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
       <c r="D13" s="6"/>
@@ -2414,7 +2414,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="7"/>
     </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
       <c r="D14" s="6"/>
@@ -2434,7 +2434,7 @@
       <c r="S14" s="6"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
       <c r="D15" s="6"/>
@@ -2454,7 +2454,7 @@
       <c r="S15" s="6"/>
       <c r="T15" s="7"/>
     </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="6"/>
@@ -2474,7 +2474,7 @@
       <c r="S16" s="6"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
@@ -2494,7 +2494,7 @@
       <c r="S17" s="6"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="6"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
@@ -2514,7 +2514,7 @@
       <c r="S18" s="6"/>
       <c r="T18" s="7"/>
     </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="6"/>
       <c r="C19" s="7"/>
       <c r="D19" s="6"/>
@@ -2534,7 +2534,7 @@
       <c r="S19" s="6"/>
       <c r="T19" s="7"/>
     </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
       <c r="D20" s="6"/>
@@ -2554,7 +2554,7 @@
       <c r="S20" s="6"/>
       <c r="T20" s="7"/>
     </row>
-    <row r="21" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
       <c r="D21" s="6"/>
@@ -2574,7 +2574,7 @@
       <c r="S21" s="6"/>
       <c r="T21" s="7"/>
     </row>
-    <row r="22" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
       <c r="D22" s="6"/>
@@ -2594,7 +2594,7 @@
       <c r="S22" s="6"/>
       <c r="T22" s="7"/>
     </row>
-    <row r="23" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="6"/>
       <c r="C23" s="7"/>
       <c r="D23" s="6"/>
@@ -2614,7 +2614,7 @@
       <c r="S23" s="6"/>
       <c r="T23" s="7"/>
     </row>
-    <row r="24" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="6"/>
@@ -2634,7 +2634,7 @@
       <c r="S24" s="6"/>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="6"/>
       <c r="C25" s="7"/>
       <c r="D25" s="6"/>
@@ -2654,7 +2654,7 @@
       <c r="S25" s="6"/>
       <c r="T25" s="7"/>
     </row>
-    <row r="26" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="8"/>
       <c r="C26" s="9">
         <f>SUM(C4:C25)</f>
@@ -2702,7 +2702,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="29" spans="2:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="12" t="s">
         <v>58</v>
       </c>

--- a/크아템.xlsx
+++ b/크아템.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소프트웨어\GIT\caweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03ADA1A4-95D9-4592-ADB1-3F29DDA55D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D730AF3-4844-459B-9952-0A372625D8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
+    <workbookView xWindow="4590" yWindow="645" windowWidth="22590" windowHeight="14835" xr2:uid="{0DBD64A1-9305-4661-A73C-3E5102D29E46}"/>
   </bookViews>
   <sheets>
     <sheet name="판매" sheetId="2" r:id="rId1"/>
@@ -1337,11 +1337,11 @@
       <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="7">
-        <v>12000</v>
+      <c r="K8" s="15">
+        <v>9000</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>34</v>
@@ -1399,11 +1399,11 @@
       <c r="C10" s="7">
         <v>10000</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="7">
-        <v>6000</v>
+      <c r="E10" s="15">
+        <v>7000</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
@@ -1566,11 +1566,11 @@
     <row r="15" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="7">
-        <v>5000</v>
+      <c r="E15" s="15">
+        <v>4000</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7"/>
@@ -1839,7 +1839,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="9">
         <f>SUM(K4:K25)</f>
-        <v>35500</v>
+        <v>32500</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="9">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C29" s="13">
         <f>SUM(B26:S26)</f>
-        <v>382000</v>
+        <v>379000</v>
       </c>
     </row>
   </sheetData>
